--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A L P</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Logan, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2334484c3690385</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8dcb5b8c38b1f3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Logan, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8dcb5b8c38b1f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6880377961dd34c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8d81da2675f09a</t>
+          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ecea7854c84d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadc8b3152de6edf</t>
+          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09f0cc3c3e322d55</t>
+          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6563c9072cece55</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a5eb12bfa24145</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0d2d6a3f455ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d966b7a2dd95df</t>
+          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d11ebfcd28367ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbb1511f618cabf</t>
+          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2db0377bd2033218</t>
+          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb233ed89e926ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5732e090675323b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5554c8b262ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=321d41ed26b61c51</t>
+          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8dbba670528e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb2fb6f6ffa31a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b713e6ebe771c3</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0d92cfd23c289</t>
+          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea0bc8d88a85d44</t>
+          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227f56442e77932a</t>
+          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c330d3407d356dad</t>
+          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac530f7ffd36eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a50b063d1b2b89</t>
+          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9122b799e128dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2364dd118caf1a52</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a457603f4b679a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3fae432856abbb</t>
+          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605f88116d6b43b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd90302f7439c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5076d2c13ddf5d3</t>
+          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14187c0426ae0fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98da314a69e75f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86465adf9c646cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72ac04a60f4d162</t>
+          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141d40bfe20c12e8</t>
+          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94375b5d9e7cae99</t>
+          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c2cd5621dd40bb</t>
+          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589547b629f51343</t>
+          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37caaacce8d7ce07</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a13b839782ca75</t>
+          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96620e34867483df</t>
+          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d543eb6b3aa6442</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e6ad85a494486</t>
+          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aca591c0990d287</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0db06ec1b0cb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a46b57ca5d88d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2524ec035ff2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d05c90daafadf3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5834374e4863cc</t>
+          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69224637a7d705fa</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2e1a31907db35</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdad3de4918ac39</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcfff1f54bd57bb</t>
+          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678a91e6ce1e590b</t>
+          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e82f243cf6d372</t>
+          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf997269e2e10bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,75 +2701,40 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a413fb586ebb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, ETL, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77c3f0c49614639e</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Engineer -.NET</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2705,41 +2705,6 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Engineer -.NET</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=613a3090cae4237e</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,33 +573,138 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Senior Software Engineer New</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Convey</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a7e1e1ef2ff4bf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Engineer New</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Convey</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f0c38e749fbda51</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Specialist, Data Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Columbus, OH, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D8" t="n">
         <v>11.1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,41 +672,6 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Specialist, Data Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Nationwide Mutual Insurance Company</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e118e0038cca00a8</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,6 +675,76 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Business Continuity</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de2646ff99b8282b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Azure Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f9c6210edfe81ce</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,40 +706,75 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2646ff99b8282b</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Business Continuity</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de2646ff99b8282b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Senior Azure Engineer</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>IQZ SYSTEMS</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>10.4</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8f9c6210edfe81ce</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer New</t>
+          <t>Software Engineer tags.new</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7e1e1ef2ff4bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0c38e749fbda51</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer New</t>
+          <t>Senior Software Engineer tags.new</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0c38e749fbda51</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7e1e1ef2ff4bf9</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,147 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2646ff99b8282b</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Business Continuity</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de2646ff99b8282b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Senior Azure Engineer</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>IQZ SYSTEMS</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8f9c6210edfe81ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2646ff99b8282b</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9c6210edfe81ce</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Technology Architect Azure platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,15 +871,50 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer tags.new</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0c38e749fbda51</t>
+          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer tags.new</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7e1e1ef2ff4bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technology Architect Azure platform</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,40 +881,215 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Azure Databricks Senior Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>.NET Backend Developer (ERP Experience Preferred)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Softengine</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Azure Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Technology Architect Azure platform</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>American business solutions inc</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D19" t="n">
         <v>10.4</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
+          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>.NET Backend Developer (ERP Experience Preferred)</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Loveland, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=19dbe4103504c9e7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Technology Architect Azure platform</t>
+          <t>.NET Backend Developer (ERP Experience Preferred)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Technology Architect Azure platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,15 +1081,85 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a44f31ac4940b0d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1483610ca5ce64</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a76068c88e5733f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Loveland, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dbe4103504c9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>.NET Backend Developer (ERP Experience Preferred)</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
+          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technology Architect Azure platform</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,75 +1091,355 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Sr Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nutrien</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Loveland, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19dbe4103504c9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Avature</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4414e81252a871d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>.NET Backend Developer (ERP Experience Preferred)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Softengine</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Azure Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Technology Architect Azure platform</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Full Stack Magento Developer – Remote (Canada)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jarvis Recruitment</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e6328c1040c5967</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>American business solutions inc</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D29" t="n">
         <v>10.4</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
+          <t>https://www.indeed.com/viewjob?jk=e080e266216f7f2e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
+          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Loveland, CO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dbe4103504c9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Loveland, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4414e81252a871d7</t>
+          <t>https://www.indeed.com/viewjob?jk=19dbe4103504c9e7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>.NET Backend Developer (ERP Experience Preferred)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
+          <t>https://www.indeed.com/viewjob?jk=4414e81252a871d7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>.NET Backend Developer (ERP Experience Preferred)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Softengine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Technology Architect Azure platform</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Magento Developer – Remote (Canada)</t>
+          <t>Technology Architect Azure platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jarvis Recruitment</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6328c1040c5967</t>
+          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,15 +1431,85 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Full Stack Magento Developer – Remote (Canada)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Jarvis Recruitment</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e6328c1040c5967</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>Senior Data Engineer (1043) - DataSF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a44f31ac4940b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>GenAI Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Spark, Kafka, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1483610ca5ce64</t>
+          <t>https://www.indeed.com/viewjob?jk=e014fe941f1f22ec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a76068c88e5733f</t>
+          <t>https://www.indeed.com/viewjob?jk=31ba26cff0eff16a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=dce2730f22d939ec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=1a44f31ac4940b0d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080e266216f7f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1483610ca5ce64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a76068c88e5733f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>First Command Financial Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e080e266216f7f2e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solutions Architect - Revo Health</t>
+          <t>Senior Software Engineer New</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Revo Health LLC.</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
+          <t>https://www.indeed.com/viewjob?jk=f5324f4c6c59141c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Software Engineer New</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nutrien</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Loveland, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dbe4103504c9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=121b212372d04928</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4414e81252a871d7</t>
+          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>.NET Backend Developer (ERP Experience Preferred)</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Softengine</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>Solutions Architect - Revo Health</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Revo Health LLC.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Technology Architect Azure platform</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Nutrien</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Loveland, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,75 +1441,460 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=19dbe4103504c9e7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Magento Developer – Remote (Canada)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jarvis Recruitment</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6328c1040c5967</t>
+          <t>https://www.indeed.com/viewjob?jk=4414e81252a871d7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Enterprise Azure Data Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ValueBase Consulting</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Trumbull, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfbd690b76118449</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>.NET Backend Developer (ERP Experience Preferred)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Softengine</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>kp reddy</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>kp reddy</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Engineer - Amazon Connect</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Oncourse Home Solutions</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Naperville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Azure Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Technology Architect Azure platform</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Full Stack Magento Developer – Remote (Canada)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Jarvis Recruitment</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e6328c1040c5967</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>American business solutions inc</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D42" t="n">
         <v>10.4</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - West</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf94c93449dfa3d</t>
+          <t>https://www.indeed.com/viewjob?jk=074ebeab3093055c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - Central</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23fa7ab7f29d61af</t>
+          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Senior Data Engineer (1043) - DataSF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff8fbb8c2cb45e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Associate - Data Engineer - Global Master Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1621e6d7e730c79</t>
+          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (1043) - DataSF</t>
+          <t>IT Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>National Retail Systems, Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lyndhurst, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=012bacb5fe848397</t>
+          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Data Platform Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Retail Systems, Inc</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lyndhurst, NJ, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da5376ea9ed63ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4423f4c3dd145f17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer - Global Master Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Trust Technology Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>Lambda, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326b602342da8867</t>
+          <t>https://www.indeed.com/viewjob?jk=ce96db4f29cbf55a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GenAI Architect</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Spark, Kafka, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e014fe941f1f22ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ba26cff0eff16a</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, dbt, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce2730f22d939ec</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a44f31ac4940b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1483610ca5ce64</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Engineer New</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, RDS, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a76068c88e5733f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5324f4c6c59141c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Software Engineer New</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=121b212372d04928</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Databricks Senior Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>First Command Financial Services</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Scala, Oracle, SQL Server, NoSQL, Data Modeling, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080e266216f7f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer New</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>kp reddy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5324f4c6c59141c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer - Amazon Connect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Oncourse Home Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad7acbb70aad17a</t>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer New</t>
+          <t>Senior Azure Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>IQZ SYSTEMS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=121b212372d04928</t>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Business Intelligence (BI) Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=166c9d26347adcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,635 +1266,40 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91b38c28583e38a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Solutions Architect - Revo Health</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Revo Health LLC.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bloomington, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, SQL Server, PostgreSQL, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18cfd44c5eb59653</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BakerHostetler</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9840944141fbe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Azure Databricks Senior Developer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Cognizant Technology Solutions</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sr Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Nutrien</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Loveland, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19dbe4103504c9e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Avature</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4414e81252a871d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Enterprise Azure Data Architect</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ValueBase Consulting</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Trumbull, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbd690b76118449</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer (ERP Experience Preferred)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Softengine</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0431d35c1c1fb538</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software Engineer - Full Stack</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>kp reddy</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Engineer - Full Stack</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>kp reddy</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Engineer - Amazon Connect</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Oncourse Home Solutions</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Naperville, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Azure Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>IQZ SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>S&amp;O Developer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Technology Architect Azure platform</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>IQZ SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4454ab3187398b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d79996f851036ab7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Full Stack Magento Developer – Remote (Canada)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Jarvis Recruitment</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6328c1040c5967</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Data Warehouse/BI Developer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>American business solutions inc</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>

--- a/results/job_matches_2026-02-23.xlsx
+++ b/results/job_matches_2026-02-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Architect, Service &amp; Operational Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c82df1ac5ad3ee0a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd06b655c3730ee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RollKall</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Oracle, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
+          <t>https://www.indeed.com/viewjob?jk=f15a9458813e7e74</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e566377201b9121f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Corteva Agriscience</t>
+          <t>RollKall</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Dataflow, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
+          <t>https://www.indeed.com/viewjob?jk=68db2c37ad6b9984</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer New</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5324f4c6c59141c</t>
+          <t>https://www.indeed.com/viewjob?jk=54c8deff754c16fa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer New</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Corteva Agriscience</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=121b212372d04928</t>
+          <t>https://www.indeed.com/viewjob?jk=84bbb3c9d11dfa7f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
+          <t>Senior Software Engineer New</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5324f4c6c59141c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Developer</t>
+          <t>Software Engineer New</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+          <t>https://www.indeed.com/viewjob?jk=121b212372d04928</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Security Engineer – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+          <t>https://www.indeed.com/viewjob?jk=5d4ac754da67252d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>SAP FICO Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kp reddy</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hilliard, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+          <t>https://www.indeed.com/viewjob?jk=98bb9f1b5eac151a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer - Amazon Connect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Oncourse Home Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+          <t>https://www.indeed.com/viewjob?jk=65d238209415bd35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+          <t>https://www.indeed.com/viewjob?jk=08527261a275aa62</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Azure Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IQZ SYSTEMS</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+          <t>https://www.indeed.com/viewjob?jk=dc66fc514f39b781</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence (BI) Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+          <t>https://www.indeed.com/viewjob?jk=003cc1fe2c6f4d82</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,40 +1266,705 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+          <t>https://www.indeed.com/viewjob?jk=ceeb3d3f63ddd02b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chesterfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6394fdb64160187b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lewisville, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bf2ba0a6a2d2ef7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c579e60e29085a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9566bb3277fc5b3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rogers, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b988c6d60df206b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40ae88bd702dcb13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rogers, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e490a596b2e349ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Klaxontech</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3338634535b9e4d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Azure Databricks Senior Developer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754f275108d306b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IvoryCloud</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=180dbcd7c9c036ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Risk Adjustment Sr. Data Analyst - Remote</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Datavant</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d255eff083655ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>kp reddy</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15451134c42bdf64</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>kp reddy</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3288093ad8485f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Engineer - Amazon Connect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Oncourse Home Solutions</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Naperville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, DynamoDB, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afb4d3e843ce82f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Cloud Storage, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3bd2134994ec718</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Azure Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>IQZ SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dce914fdc34a1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fanatics</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1be8fdec648472af</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence (BI) Developer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Radiant Digital</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chesterfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776eaa52cad25247</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329bc88cd35a3445</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>American business solutions inc</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D44" t="n">
         <v>10.4</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=18ade4abca790417</t>
         </is>
